--- a/src/attributions/attributions_ig_traj_87.xlsx
+++ b/src/attributions/attributions_ig_traj_87.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.05782103381392111</v>
+        <v>0.3050205088513453</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1184983161518482</v>
+        <v>-0.2062432042482076</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007669583920453605</v>
+        <v>-0.08305761052070644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0708227507335234</v>
+        <v>0.3951416155210238</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09221441129909404</v>
+        <v>-0.1094410502894071</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1616,40 +1616,40 @@
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05686669664795709</v>
+        <v>-0.08094873654513306</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02327631916354174</v>
+        <v>-0.01735055220801952</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01344786068610653</v>
+        <v>-0.226148551717799</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0006130210446103036</v>
+        <v>-0.01826588986519356</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.002427187119212746</v>
+        <v>0.0965681546346924</v>
       </c>
       <c r="AC3" t="n">
         <v>-0</v>
@@ -1658,25 +1658,25 @@
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.02462358337218798</v>
+        <v>-0.1105058827142829</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.007197644092550807</v>
+        <v>0.05553587003343709</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.002280776272955634</v>
+        <v>-0.009080472354300264</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1685,10 +1685,10 @@
         <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.002304981216569174</v>
+        <v>0.0147699225136713</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1700,37 +1700,37 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.002809322391113558</v>
+        <v>-0.00114355794886966</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.01789724272017127</v>
+        <v>0.1563147788890615</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.3097006852112607</v>
+        <v>-0.0481744504170465</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.03750511814922747</v>
+        <v>-0.03739001114103444</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.05165502058316458</v>
+        <v>0.08533506649465014</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1180355637155186</v>
+        <v>-0.2161349377638919</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.08532641644254794</v>
+        <v>0.007255212955539959</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02016902748087887</v>
+        <v>-0.07892888685549551</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,34 +1769,34 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1134932973926774</v>
+        <v>0.08320029623565212</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.07316155536950859</v>
+        <v>0.0703824300922218</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.03168425935470709</v>
+        <v>0.1398307646735128</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1226165324007316</v>
+        <v>-0.2623813463300373</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1808,91 +1808,91 @@
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.05871905673892709</v>
+        <v>-0.0419585180549098</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.04288333359930822</v>
+        <v>-0.2417310608719461</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.04478501875317428</v>
+        <v>0.1372192475990445</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.01151308384433546</v>
+        <v>0.06005354231914467</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.04628912205528526</v>
+        <v>-0.2176368354127701</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.07210459168992829</v>
+        <v>0.1963714280503098</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1122402573683366</v>
+        <v>-0.09104311188856203</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.03657086845468677</v>
+        <v>-0.2189781442061692</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.04092858490708869</v>
+        <v>0.1050358690000621</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.00460715855327617</v>
+        <v>0.05712129146258952</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.01888396078661333</v>
+        <v>-0.220903681446028</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -1901,37 +1901,37 @@
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05078837594803452</v>
+        <v>0.1463637683334791</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.04984907647849025</v>
+        <v>0.08272440058601682</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.008515814953660232</v>
+        <v>-0.1532147873177299</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.03546662624985097</v>
+        <v>0.3263121273312532</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,16 +1940,16 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0.001137662205916876</v>
+        <v>0.04136928250931749</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.01032966626223772</v>
+        <v>0.0276992274829155</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
@@ -1958,49 +1958,49 @@
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1182502696294432</v>
+        <v>0.2736506935767779</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.04902328611129859</v>
+        <v>-0.003867883087236433</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.05019108772074419</v>
+        <v>-0.1018932819506565</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.04137788598828828</v>
+        <v>0.04051440365403586</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02905101575506604</v>
+        <v>0.1027060366468447</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.02483060506371284</v>
+        <v>0.1185498983510546</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2009,52 +2009,52 @@
         <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1557291030676286</v>
+        <v>0.2888643650003276</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.03353237434383261</v>
+        <v>-0.1228663427771521</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.03733848486822192</v>
+        <v>-0.2186311589717385</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.06012071000588442</v>
+        <v>0.1020181938249407</v>
       </c>
       <c r="FC3" t="n">
         <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.008014452227952384</v>
+        <v>0.04831979701707246</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.00864123749341956</v>
+        <v>-0.2733522382689271</v>
       </c>
       <c r="FH3" t="n">
         <v>-0</v>
@@ -2066,22 +2066,22 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.07540666769935146</v>
+        <v>0.2495237363237856</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.01900288572380196</v>
+        <v>-0.0722031349811034</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.02628883103839198</v>
+        <v>-0.032408225674953</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
@@ -2090,13 +2090,13 @@
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04683419305527916</v>
+        <v>0.0787374797228667</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
@@ -2105,19 +2105,19 @@
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.1254109141309285</v>
+        <v>0.297178647780563</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.03019127009283162</v>
+        <v>-0.02910206220322056</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>0</v>
@@ -2126,13 +2126,13 @@
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0.02894884775782244</v>
+        <v>-0.07148855981189485</v>
       </c>
     </row>
     <row r="4">
@@ -2706,19 +2706,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3669361561895835</v>
+        <v>0.9538134318474287</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1093932445150783</v>
+        <v>-0.4223919311667668</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.070254589433157</v>
+        <v>-0.144005924155271</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,28 +2727,28 @@
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2784501494973319</v>
+        <v>0.8704591350574266</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09954262336451403</v>
+        <v>-0.5398132477320252</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06701759020103108</v>
+        <v>-0.258117578845249</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
@@ -2760,73 +2760,73 @@
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1086816962778712</v>
+        <v>0.09685943873462502</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.006641105985647352</v>
+        <v>0.06461894753613788</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0054614967710381</v>
+        <v>-0.07714139909583445</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.08166235920496939</v>
+        <v>-5.922295313760985e-05</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01746021374381788</v>
+        <v>-0.2796388141269585</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.03265214553187715</v>
+        <v>-0.02128783432771526</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01447320767688632</v>
+        <v>0.08589002561017008</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.00528044804860744</v>
+        <v>0.007526923350603159</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.004718096684488767</v>
+        <v>0.03207131914869883</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2844,73 +2844,73 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3888104826248379</v>
+        <v>0.8605077459617945</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01461599785790184</v>
+        <v>-0.2385398907655246</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.03568650419229344</v>
+        <v>-0.1781565053971929</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03343057868388861</v>
+        <v>0.1532481156918161</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.06285445957526954</v>
+        <v>-0.009517336713876496</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1389957400628531</v>
+        <v>-0.0406443100494131</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02913879144707355</v>
+        <v>-0.3122809799001593</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.08501858759881707</v>
+        <v>0.008116222644460686</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.149428298332094</v>
+        <v>0.1598280107807011</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2922,76 +2922,76 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1638383275043859</v>
+        <v>0.5201645692986145</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.005544707154968637</v>
+        <v>-0.2521411578233797</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0229773520153302</v>
+        <v>0.07283071602839691</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1223727877167004</v>
+        <v>-0.4578932072917591</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02862292155678853</v>
+        <v>0.334553651605822</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.02467698096670003</v>
+        <v>-0.003653439419459024</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.01490418572833391</v>
+        <v>-0.3392905442475606</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.05886803506514758</v>
+        <v>0.2824338544819991</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1239877204150062</v>
+        <v>-0.1664118597522651</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
@@ -3000,25 +3000,25 @@
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1037681499964938</v>
+        <v>-0.4314938378788076</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.05901684044864009</v>
+        <v>0.3014126240306447</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03049954457059622</v>
+        <v>0.05087864442467625</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3027,109 +3027,109 @@
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1269445035284396</v>
+        <v>-0.2373939703840524</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.05978967963315184</v>
+        <v>0.04718697511388301</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.006750166833388262</v>
+        <v>-0.2500574843025496</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.02122585012315931</v>
+        <v>0.2757588567864447</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0911268301918063</v>
+        <v>-0.2011617241621149</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02987145370559912</v>
+        <v>0.01711230690147475</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1029817128325021</v>
+        <v>0.02304496571890338</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.05143027728635843</v>
+        <v>0.2358160851627996</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01805593078157746</v>
+        <v>0.1921661865364035</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1185215910568478</v>
+        <v>-0.368532436206809</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.05770004052376736</v>
+        <v>0.2574297099951681</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0665277163825288</v>
+        <v>0.129772175184957</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -3141,22 +3141,22 @@
         <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.07886678601048838</v>
+        <v>-0.1987349712983795</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.04425140409435679</v>
+        <v>0.05026406016806367</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.005057629757954684</v>
+        <v>-0.09537630627877904</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,73 +3165,73 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1146807061354856</v>
+        <v>-0.4801076496452996</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.03764017130051954</v>
+        <v>0.3492163144226501</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02860412472656454</v>
+        <v>-0.03042570005220837</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02154107917937501</v>
+        <v>-0.2942409747618515</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.03483302131967833</v>
+        <v>0.1475574468737782</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.07199457362965607</v>
+        <v>-0.1889654611465242</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.027241873090211</v>
+        <v>-0.5053904635465443</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.08298676836853067</v>
+        <v>0.6963295312256329</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.006230754682081649</v>
+        <v>0.1305252102411159</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3240,34 +3240,34 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.03854225614765504</v>
+        <v>-0.4685363263055368</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.05599999484930872</v>
+        <v>0.2111252995830971</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3278,19 +3278,19 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1787395930380023</v>
+        <v>0.5774229668012804</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1088426158490149</v>
+        <v>0.05813702997011983</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02391038132941505</v>
+        <v>-0.2411883238618052</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -3299,82 +3299,82 @@
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.126962353710824</v>
+        <v>0.6380839820445708</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09836902670017375</v>
+        <v>-0.08778161728040504</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02791122905680323</v>
+        <v>-0.1873703040363826</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0403325190599523</v>
+        <v>0.09239663035909361</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0509396825864603</v>
+        <v>-0.08678599668008005</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003281753905763671</v>
+        <v>-0.07039690307351426</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06098821518447527</v>
+        <v>0.01862624889386821</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01738250495095807</v>
+        <v>-0.1578239143455234</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.02869289419281348</v>
+        <v>-0.005951472263230433</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
@@ -3386,46 +3386,46 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0180830031094323</v>
+        <v>0.05341973528347729</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003163441612190647</v>
+        <v>0.01460627875685593</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.003763633613631166</v>
+        <v>-0.006784717227577257</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2673339832397049</v>
+        <v>0.7838470073338535</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01152224064777276</v>
+        <v>-0.1201853279496791</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.008530169988111794</v>
+        <v>-0.1044853517476319</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
@@ -3434,40 +3434,40 @@
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01680099174624125</v>
+        <v>-0.01154797183907411</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1186591194408441</v>
+        <v>-0.05072275897878469</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.009139555358859497</v>
+        <v>-0.144534121766142</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.09393984162623296</v>
+        <v>-0.05634309317160161</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.06050197688775651</v>
+        <v>0.1259066955905649</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.06425722223933314</v>
+        <v>0.04975272901471668</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3488,25 +3488,25 @@
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.07884649805523389</v>
+        <v>0.3186987871398222</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.008602640409626062</v>
+        <v>-0.02042328010331015</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.003439513547878237</v>
+        <v>-0.1653427447960825</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,13 +3515,13 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.04588231194069816</v>
+        <v>-0.2684699524616966</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,13 +3530,13 @@
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.02180987620984302</v>
+        <v>-0.02188143705096069</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.008054241559913093</v>
+        <v>0.1354457002187822</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,55 +3545,55 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.01283913192136074</v>
+        <v>-0.1649888216880985</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.03916726113770775</v>
+        <v>0.1034585480004947</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.05449586815528324</v>
+        <v>0.1380112834850243</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.03476169652064544</v>
+        <v>-0.2589419938538614</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01513077768719239</v>
+        <v>-0.0134888791416734</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02799826851385519</v>
+        <v>0.1512149920057948</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
@@ -3602,73 +3602,73 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.05469790982245256</v>
+        <v>-0.09948139950457617</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.112025370380135</v>
+        <v>-0.2511065353723218</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.007333740554528179</v>
+        <v>0.07237984811391322</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.02824425791666936</v>
+        <v>0.06725120002797196</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.1202322149007</v>
+        <v>0.07277468851464801</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.05984439378903247</v>
+        <v>-0.03585000813569923</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.03402834958176885</v>
+        <v>-0.04606417488844401</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.04215864806433086</v>
+        <v>-0.08483509629562025</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.007349943967966143</v>
+        <v>0.06000775970062225</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3680,25 +3680,25 @@
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.05257353350409371</v>
+        <v>-0.1730532465093049</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
         <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02596757810287468</v>
+        <v>-0.03446323593017502</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.007380004933911552</v>
+        <v>0.09235088607301663</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,37 +3707,37 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.04136714109975363</v>
+        <v>-0.1194296044828924</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02217862592491426</v>
+        <v>-0.09721946351415402</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0260800023054365</v>
+        <v>0.06037378040327473</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.03265420290069151</v>
+        <v>-0.2787865851079636</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,52 +3746,52 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.008116648669383539</v>
+        <v>-0.08042092644952906</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03103368316022166</v>
+        <v>0.1275705132941846</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.011426994595209</v>
+        <v>-0.2709704809614792</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.1071594718452163</v>
+        <v>0.07893549695544602</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02999548327284006</v>
+        <v>0.2141071640907778</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.003504930960095492</v>
+        <v>-0.3025044628142554</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,37 +3800,37 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0358529970349898</v>
+        <v>-0.07916605076818876</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0250018494895706</v>
+        <v>0.01719638911803971</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.015390829662191</v>
+        <v>-0.1540887581829769</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.0499096768604104</v>
+        <v>0.1167439364714681</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,24 +3839,24 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.5710610100654896</v>
+        <v>-0.626896956594268</v>
       </c>
       <c r="C7" t="n">
         <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7867220109347699</v>
+        <v>0.5030194044573433</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05767748884857922</v>
+        <v>0.1539024421195778</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
@@ -3871,22 +3871,22 @@
         <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6328133826578226</v>
+        <v>-0.7955590673127391</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6691117246843684</v>
+        <v>0.699880318078261</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02701060574266098</v>
+        <v>0.2549881763881801</v>
       </c>
       <c r="O7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2130628585462578</v>
+        <v>-0.07499683593914154</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1726406522888515</v>
+        <v>-0.02029702596237921</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01320336910466791</v>
+        <v>0.09202656523510325</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>-0</v>
@@ -3928,25 +3928,25 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.1055131795002467</v>
+        <v>-0.03631108113094121</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1221668042147674</v>
+        <v>0.1059580166400123</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.002353479197424928</v>
+        <v>-0.02924114430693678</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
         <v>-0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.03177410095376651</v>
+        <v>-0.06973111423644122</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02977974563350919</v>
+        <v>0.02203373128664069</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.05024616571606411</v>
+        <v>-0.1058180077816263</v>
       </c>
       <c r="AP7" t="n">
         <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3982,46 +3982,46 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.260859917939103</v>
+        <v>-0.5467421189137599</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.4299763334386236</v>
+        <v>0.3786858169196117</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07365453871585737</v>
+        <v>0.2695442219077348</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.2598132636131383</v>
+        <v>0.07661595014504208</v>
       </c>
       <c r="BE7" t="n">
         <v>-0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.2775018017656317</v>
+        <v>-0.01957437892076091</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.06356354802687918</v>
+        <v>0.06819209785058696</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI7" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.1285904638036987</v>
+        <v>0.1637954738969382</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01824372255732868</v>
+        <v>-0.05577144436133985</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.2405191888608533</v>
+        <v>-0.06018642558558322</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.2203305192804413</v>
+        <v>-0.5707914245060184</v>
       </c>
       <c r="BW7" t="n">
         <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.2269166497629692</v>
+        <v>0.3290948045644236</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.05191731893230175</v>
+        <v>0.03262689971089631</v>
       </c>
       <c r="BZ7" t="n">
         <v>-0</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
@@ -4090,100 +4090,100 @@
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.1417340159456186</v>
+        <v>0.350389222168988</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.2359970266736811</v>
+        <v>-0.2643189201556154</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01391653284701731</v>
+        <v>0.01055835445983144</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
         <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.06853784539395925</v>
+        <v>0.229408624052636</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.04770617509845362</v>
+        <v>-0.2526594906661911</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.09418519245549316</v>
+        <v>-0.0006477042778293168</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.1636392829013889</v>
+        <v>0.3465426869732476</v>
       </c>
       <c r="CX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.2388736011773729</v>
+        <v>-0.2506341749128197</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.03304293974325675</v>
+        <v>-0.03575298007854628</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
         <v>-0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.4270296772777524</v>
+        <v>0.2117732476438931</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.2370141223885918</v>
+        <v>-0.1068712133443791</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01142354327050209</v>
+        <v>0.1521465234537694</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK7" t="n">
         <v>-0</v>
@@ -4192,25 +4192,25 @@
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07558171485498025</v>
+        <v>-0.2234793704655637</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.01626831951625442</v>
+        <v>-0.1270096714158988</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.1271289858118855</v>
+        <v>-0.05156808132375932</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
         <v>0</v>
@@ -4222,46 +4222,46 @@
         <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.1322265404224444</v>
+        <v>0.008548116784875806</v>
       </c>
       <c r="DY7" t="n">
         <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.1812627763501342</v>
+        <v>-0.1083055243684906</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.1089048325202479</v>
+        <v>-0.01119771555232253</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.1323552665266542</v>
+        <v>0.3210195769503946</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.181507610537496</v>
+        <v>-0.2548024934008185</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0786435717981126</v>
+        <v>-0.06925886943041959</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
@@ -4273,28 +4273,28 @@
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.1438019977068809</v>
+        <v>0.1486444772651049</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1618902010857386</v>
+        <v>0.1320672000982182</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.02207805993232079</v>
+        <v>0.003415194404203673</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV7" t="n">
         <v>-0</v>
@@ -4306,43 +4306,43 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.1588771865785356</v>
+        <v>0.3812667959167123</v>
       </c>
       <c r="EZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.2253126773938929</v>
+        <v>-0.2855401017375105</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.004218015674084093</v>
+        <v>0.01065866227215642</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.0327326198334304</v>
+        <v>0.2042638750578912</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.06662547232018297</v>
+        <v>-0.1239038419897797</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01754923719882058</v>
+        <v>0.07317768406777454</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,28 +4351,28 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.02958571151617876</v>
+        <v>0.4105011957897304</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.05908328565926025</v>
+        <v>-0.5528187677048506</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04646481182168466</v>
+        <v>-0.1944123659453458</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1655808646434501</v>
+        <v>0.3055304087093481</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.08154349777732789</v>
+        <v>-0.1536394746613499</v>
       </c>
       <c r="GC7" t="n">
         <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE7" t="n">
         <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,43 +4416,43 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2862637016072813</v>
+        <v>0.8858119446324533</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04097696718559241</v>
+        <v>-0.5145066456561137</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06085675972085831</v>
+        <v>-0.14223232922036</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1760304123496681</v>
+        <v>0.9580502249861799</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0582075208589317</v>
+        <v>-0.6882153638794395</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04915610883062645</v>
+        <v>-0.212595047135568</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4470,151 +4470,151 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05593480653934985</v>
+        <v>0.1074342730254463</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.02509420395121988</v>
+        <v>-0.06617567945911058</v>
       </c>
       <c r="W8" t="n">
-        <v>0.031689575048028</v>
+        <v>-0.1046696597438078</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0178121793060576</v>
+        <v>0.2164275999023088</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01435249058933597</v>
+        <v>-0.1833378963439869</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01398696265237206</v>
+        <v>0.2199890871942968</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.00333812448066348</v>
+        <v>0.09938611942837262</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.01308755329425176</v>
+        <v>-0.05790205474902903</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02665638569540443</v>
+        <v>0.1034124549025221</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2708956380358412</v>
+        <v>1.018916168778098</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.04625264421900929</v>
+        <v>-0.3555694712402943</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.05796202521849612</v>
+        <v>-0.2383803532000989</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02667144123427052</v>
+        <v>-0.03316703181037</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.07264072797270622</v>
+        <v>-0.06059762448715184</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.08293278335695409</v>
+        <v>-0.08473130510661393</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1139639515938697</v>
+        <v>-0.02936408343834</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0238771169643599</v>
+        <v>0.05256977466146569</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1329727499433681</v>
+        <v>0.2231432808609672</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4629,46 +4629,46 @@
         <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1139588775670142</v>
+        <v>0.5152417613029915</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.02257531261892639</v>
+        <v>-0.2389299841429428</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03934894528117207</v>
+        <v>-0.001033607988512432</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.07310028582391566</v>
+        <v>-0.3763003542011681</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.002476227497223638</v>
+        <v>0.3275892558182164</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01013487447202625</v>
+        <v>-0.008617791431356917</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
@@ -4680,76 +4680,76 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.009470431725747696</v>
+        <v>-0.3310883383756708</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.0366206016958569</v>
+        <v>0.31163614415816</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.0658558757234018</v>
+        <v>-0.1349150383739688</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.06096125376798028</v>
+        <v>-0.3710139158136908</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.008738062859503772</v>
+        <v>0.3331775872752136</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01053041254814411</v>
+        <v>0.02303940192783979</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.08271591037153254</v>
+        <v>-0.2022165260369196</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.05951106953603558</v>
+        <v>0.1240972880089512</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04736489305726618</v>
+        <v>-0.1478832706488087</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
@@ -4764,28 +4764,28 @@
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.03532664897396813</v>
+        <v>-0.2342498713416261</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.06682067971022781</v>
+        <v>-0.2793571437916971</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.0187535824475111</v>
+        <v>-0.1136666619322292</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,43 +4794,43 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.07233841944566825</v>
+        <v>-0.2403620268870107</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.03562424518278044</v>
+        <v>0.1970819239845694</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.02972271388555807</v>
+        <v>0.1382990023766068</v>
       </c>
       <c r="EB8" t="n">
         <v>-0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08404529207253011</v>
+        <v>-0.3502440795882036</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.01633331798558305</v>
+        <v>0.2579363882102741</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.04314005260967468</v>
+        <v>0.1502854365639976</v>
       </c>
       <c r="EK8" t="n">
         <v>-0</v>
@@ -4839,31 +4839,31 @@
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01809486472144711</v>
+        <v>0.02724812626475434</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.01037455090411216</v>
+        <v>0.09299213573087706</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.04808133452017033</v>
+        <v>-0.0739846997723704</v>
       </c>
       <c r="ET8" t="n">
         <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,16 +4875,16 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.05995209468474148</v>
+        <v>-0.4324076067369489</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>-0.009406049361452338</v>
+        <v>0.3708547706816397</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.009317473082144312</v>
+        <v>-0.01692215889267883</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
@@ -4896,22 +4896,22 @@
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.01620001347134361</v>
+        <v>-0.1201600347607752</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.00439234059116591</v>
+        <v>0.1392270886143644</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.08150001702779987</v>
+        <v>-0.3088384400716065</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
@@ -4923,58 +4923,58 @@
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.04289751713969025</v>
+        <v>-0.6299509939117324</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.04328104183018685</v>
+        <v>0.3699317780750551</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.04594237706207796</v>
+        <v>0.3841002074817123</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
         <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01993984939575669</v>
+        <v>-0.2899903926119078</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.05777753308379101</v>
+        <v>0.2097788646643963</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
         <v>-0</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>-0</v>
@@ -4982,22 +4982,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08157445117265771</v>
+        <v>-0.07711472205878445</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02773991104305372</v>
+        <v>-0.04679063928246891</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7138586967795418</v>
+        <v>0.2315325017727111</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5009,25 +5009,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02196503866929597</v>
+        <v>-0.1090447484454636</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08792428567719135</v>
+        <v>-0.02173436784804599</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5064023815449017</v>
+        <v>0.2579734286552827</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -5036,22 +5036,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.02032178023747242</v>
+        <v>-0.01504835522718944</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09048564131888512</v>
+        <v>-0.009786406913397265</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1083057556712803</v>
+        <v>0.007696700095277983</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
         <v>-0</v>
@@ -5072,16 +5072,16 @@
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.04308367430251788</v>
+        <v>0.04300666014158853</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.003967591181657309</v>
+        <v>0.05579224717708885</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.04437300921547052</v>
+        <v>0.01365176664507868</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -5090,28 +5090,28 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.01322120709566549</v>
+        <v>0.005053988294461656</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04734620549020306</v>
+        <v>-0.01754861067795161</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.024297494587364</v>
+        <v>-0.006427038615918702</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>-0</v>
@@ -5123,43 +5123,43 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.03716295805414514</v>
+        <v>-0.03943285422901679</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.07353523209343334</v>
+        <v>-0.136756657117088</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.4703035990025237</v>
+        <v>0.1632929316866243</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01469287893533112</v>
+        <v>0.002132720460347582</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01658463466592996</v>
+        <v>0.04920161524042307</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.2296703956282711</v>
+        <v>0.01621889133759216</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
@@ -5168,10 +5168,10 @@
         <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
         <v>0</v>
@@ -5180,19 +5180,19 @@
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.1203451720228799</v>
+        <v>0.03484599433582724</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.06197953921298578</v>
+        <v>-0.09941693116257726</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0.00885961058345279</v>
+        <v>-0.03138575897461084</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
         <v>-0</v>
@@ -5207,16 +5207,16 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.009145770585844249</v>
+        <v>-0.1011822787640205</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.07822961956629404</v>
+        <v>-0.1153987911483351</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.2570292290190346</v>
+        <v>0.1111162805358234</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01995960801059368</v>
+        <v>0.02875380491267245</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02437275596725737</v>
+        <v>0.03029286195464355</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0.1972895179986878</v>
+        <v>-0.06794207544791847</v>
       </c>
       <c r="CJ9" t="n">
         <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5261,25 +5261,25 @@
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1026771891879715</v>
+        <v>0.004216546692415037</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.221369662057053</v>
+        <v>0.08711395900138266</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.06832135013920518</v>
+        <v>0.01284210629330926</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
         <v>-0</v>
@@ -5288,25 +5288,25 @@
         <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02814020882610809</v>
+        <v>0.02628109203970726</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02076390294744419</v>
+        <v>0.01521890769119472</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0.1784200693693633</v>
+        <v>-0.08902958225277137</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
         <v>-0</v>
@@ -5315,43 +5315,43 @@
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02353930069768179</v>
+        <v>0.04075930148456314</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.05177053625969878</v>
+        <v>-0.1045249551233826</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001209372722624227</v>
+        <v>0.001120040064605136</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
         <v>-0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05034425892226894</v>
+        <v>-0.01874943627071398</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02244095203059502</v>
+        <v>-0.01789934393456193</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.09086586172314379</v>
+        <v>-0.002130411309172848</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
@@ -5363,28 +5363,28 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.0130600606501928</v>
+        <v>0.02559894170570632</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.009117651671305222</v>
+        <v>0.07984845861710431</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.1251143631851139</v>
+        <v>0.09305784229169797</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
@@ -5393,19 +5393,19 @@
         <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.1032267172971268</v>
+        <v>0.05354997827955334</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04204191588599056</v>
+        <v>0.001795965143248516</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0.140781890039951</v>
+        <v>-0.015409200395082</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>0</v>
@@ -5414,34 +5414,34 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0873730888383674</v>
+        <v>0.02537893376374117</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.03303650531567804</v>
+        <v>0.09104161709334536</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.02841259329962694</v>
+        <v>-0.03922773929105778</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
         <v>0</v>
@@ -5450,100 +5450,100 @@
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0340635316743766</v>
+        <v>0.03948155503877977</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.06027992463613287</v>
+        <v>0.02391471838146874</v>
       </c>
       <c r="FC9" t="n">
-        <v>-0.1690367865409942</v>
+        <v>-0.08264765984395189</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0.04636053907436542</v>
+        <v>0.06866025301428826</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.07588877891332169</v>
+        <v>0.04248341809575366</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.113187560742503</v>
+        <v>-0.0278821370341996</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.004097854927064552</v>
+        <v>-0.02479196584698269</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.2911048135871796</v>
+        <v>0.1911105962875012</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0.07931942528978841</v>
+        <v>-0.0326156323651012</v>
       </c>
       <c r="FV9" t="n">
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.007859844987639267</v>
+        <v>0.07376076329039875</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.004600144624084024</v>
+        <v>-0.02389291095870561</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4978054477531577</v>
+        <v>0.5696425898771549</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.02543284178179592</v>
+        <v>-0.03442107634768386</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4487876237244407</v>
+        <v>-0.2651710511344799</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3947512156678576</v>
+        <v>0.9567567808696922</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.02813722356015175</v>
+        <v>-0.1958889390460547</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4829679569773103</v>
+        <v>-0.3504599897984735</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07217819164241299</v>
+        <v>0.1849511983905759</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01880314743225923</v>
+        <v>-0.1989663924666986</v>
       </c>
       <c r="X13" t="n">
-        <v>0.001446884118040624</v>
+        <v>-0.03792003355472312</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.04701037043026227</v>
+        <v>0.03561352029624793</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.04837226606425898</v>
+        <v>-0.5214205566110839</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.002403360190878657</v>
+        <v>-0.2239417500627622</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,13 +7363,13 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03301540807679167</v>
+        <v>0.06558802497277565</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.005983038903205696</v>
+        <v>-0.1135112231663808</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.06971461677939465</v>
+        <v>-0.03265930367082079</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,64 +7393,64 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3984113551274697</v>
+        <v>0.9972383026745042</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.02975964344408763</v>
+        <v>-0.1854711610134981</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.3321831170345719</v>
+        <v>-0.3485327101731728</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1612358485032645</v>
+        <v>-0.005821863095528458</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1684564900362755</v>
+        <v>-0.2138710388235801</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.203825938433831</v>
+        <v>-0.03063176025061206</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1896704572192895</v>
+        <v>0.1794117725108071</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.09536774391091286</v>
+        <v>0.1525998609938358</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0.00589424008263874</v>
+        <v>-0.0459841192241293</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,19 +7477,19 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2028834034081088</v>
+        <v>0.6135958915302765</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.0162831439929076</v>
+        <v>-0.1006401921657055</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1315335366501691</v>
+        <v>-0.1638210725502962</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7501,10 +7501,10 @@
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.09266767263866814</v>
+        <v>-0.194640011835631</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
@@ -7513,16 +7513,16 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.0300018450203258</v>
+        <v>0.07096703831037489</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08066902136464411</v>
+        <v>0.1376961581699223</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
         <v>-0</v>
@@ -7531,19 +7531,19 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.0770770976300184</v>
+        <v>-0.5970548021106392</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.05385606685156184</v>
+        <v>0.2572472488904427</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0002695365186649608</v>
+        <v>0.1593170235629695</v>
       </c>
       <c r="CS13" t="n">
         <v>0</v>
@@ -7555,10 +7555,10 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.06803360433173926</v>
+        <v>-0.1924907752346184</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,16 +7567,16 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01865709904776138</v>
+        <v>0.01035375686398623</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.07668261256850482</v>
+        <v>0.1396979468330257</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,19 +7585,19 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.1163878543974388</v>
+        <v>-0.0328092549987486</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04735058902161236</v>
+        <v>-0.3353417903165339</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.02045708295409829</v>
+        <v>-0.05341482622870019</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
@@ -7606,82 +7606,82 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03667932603747118</v>
+        <v>-0.1949095537999859</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001312173433802721</v>
+        <v>0.1800627324046425</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.02214778250564311</v>
+        <v>0.0315230305481</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.05201758299918303</v>
+        <v>0.03867655854205965</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.01582555452451458</v>
+        <v>0.2292717202265163</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.001203139130865473</v>
+        <v>-0.2107347938798646</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.04380794557249622</v>
+        <v>-0.01043824173951947</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.0005833610655655028</v>
+        <v>-0.08958370977298655</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.06287219205075538</v>
+        <v>0.09149387277322424</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7690,22 +7690,22 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.02555983524210745</v>
+        <v>0.08427213548663225</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01575307097406646</v>
+        <v>-0.1261076783760271</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.003275067688917277</v>
+        <v>0.07715339131383815</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7714,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06790478348993169</v>
+        <v>-0.2168466135843294</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.0008734905591401325</v>
+        <v>-0.004594519468679057</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.07767029976360242</v>
+        <v>0.142993158609454</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.01898360209569339</v>
+        <v>-0.2632586387446145</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,52 +7756,52 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.03724258198809156</v>
+        <v>0.2600373667472031</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.1247658251987905</v>
+        <v>0.02191300424526176</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.00623122166158553</v>
+        <v>0.05038380048076807</v>
       </c>
       <c r="FR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.05614794536113066</v>
+        <v>-0.05860022117783017</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.08078405934653415</v>
+        <v>-0.1264393942775647</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.04683394364618966</v>
+        <v>-0.02912205695842569</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.08749349469496022</v>
+        <v>0.01222384984835842</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7827,55 +7827,55 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2954890426482155</v>
+        <v>-0.3885944820338565</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3403365678572871</v>
+        <v>0.5026131063080138</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06741458260786791</v>
+        <v>0.291046064389384</v>
       </c>
       <c r="F14" t="n">
         <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2499470700757904</v>
+        <v>-0.4139626398448422</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.305443770773947</v>
+        <v>0.6838037168748731</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1503280232189548</v>
+        <v>0.4747173980101727</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
@@ -7884,70 +7884,70 @@
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03541889506676031</v>
+        <v>-0.06201303319127607</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.07559673710668868</v>
+        <v>0.08642429182972383</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1902141834435923</v>
+        <v>0.04382340951823547</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.04089166654240377</v>
+        <v>0.005930063900340574</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.02208201723438645</v>
+        <v>-0.06545455658571721</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01538754743248954</v>
+        <v>-0.1401370410642867</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.03686043408810041</v>
+        <v>-0.1694150638739923</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.01323568752154213</v>
+        <v>0.02584754196363521</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.02076907775535372</v>
+        <v>-0.1514848740089774</v>
       </c>
       <c r="AP14" t="n">
         <v>-0</v>
@@ -7965,25 +7965,25 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.3831227974750615</v>
+        <v>-0.5522488499667422</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.04625881627390258</v>
+        <v>0.116499160514928</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1165136981950207</v>
+        <v>0.244781255216356</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -7992,16 +7992,16 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.007886469598213888</v>
+        <v>0.07088984811375293</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.1469228100815287</v>
+        <v>0.1818750062260418</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.3044937697056344</v>
+        <v>0.2232221443039775</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
@@ -8019,19 +8019,19 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.005803426700631003</v>
+        <v>0.08236071550138779</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.01846450013851228</v>
+        <v>-0.08962065376506997</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.09133130546497206</v>
+        <v>-0.02650887736432825</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8040,22 +8040,22 @@
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.2370524405965062</v>
+        <v>-0.3871716114041147</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01988172522280303</v>
+        <v>0.3136818343120117</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.00265025390540502</v>
+        <v>0.1157866087728817</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8064,28 +8064,28 @@
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
         <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.08597054993291786</v>
+        <v>0.2458006282406849</v>
       </c>
       <c r="CF14" t="n">
         <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.09381800923987767</v>
+        <v>-0.1736048326086158</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.02345757694738306</v>
+        <v>-0.01866152999727631</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>0</v>
@@ -8094,25 +8094,25 @@
         <v>-0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.008942372501990505</v>
+        <v>0.2002402997339013</v>
       </c>
       <c r="CO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.006388040716170511</v>
+        <v>-0.340731713291106</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.02082437725279748</v>
+        <v>-0.1369943467285286</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
@@ -8124,19 +8124,19 @@
         <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.08289046202903248</v>
+        <v>0.2318255886474896</v>
       </c>
       <c r="CX14" t="n">
         <v>-0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.08744920610340827</v>
+        <v>-0.1922041342573305</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.005932664493183079</v>
+        <v>-0.04717608305697119</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
@@ -8151,22 +8151,22 @@
         <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.008944806317395427</v>
+        <v>0.005015128490577218</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.03224947165003563</v>
+        <v>-0.07474133001456036</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.08166682324558472</v>
+        <v>0.06998444385032034</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8178,25 +8178,25 @@
         <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.07271836072224921</v>
+        <v>0.07456739521710783</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.1390271598239578</v>
+        <v>-0.1268198475051903</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.01040567679484911</v>
+        <v>0.06567485299765607</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
@@ -8208,100 +8208,100 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.01340587232675811</v>
+        <v>-0.01850820045426781</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0144196058634867</v>
+        <v>-0.07281352838969933</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.02038591224068513</v>
+        <v>-0.1043610206416391</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
         <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.009291451841205648</v>
+        <v>0.1930675170320845</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.04322573472087581</v>
+        <v>-0.07591829613091181</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.03451927158975499</v>
+        <v>-0.1259750589832565</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
         <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.09380183399695607</v>
+        <v>0.2149910486364548</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.09220257222596551</v>
+        <v>-0.1541018566532122</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.09463479200209642</v>
+        <v>-0.05358279171179527</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.09723504039751632</v>
+        <v>0.2740442483145938</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.09879628807756567</v>
+        <v>-0.2315437505822085</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01303552426635709</v>
+        <v>-0.04490982378139648</v>
       </c>
       <c r="FC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
@@ -8316,16 +8316,16 @@
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.02642486899290284</v>
+        <v>0.177062159896793</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.01581059743828286</v>
+        <v>0.1592329719438186</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.04149955766060625</v>
+        <v>-0.07426585745534138</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8334,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,16 +8343,16 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.004953441519895944</v>
+        <v>-0.1967444836147517</v>
       </c>
       <c r="FR14" t="n">
         <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.02667896189048104</v>
+        <v>-0.16106384576571</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.03157035874066413</v>
+        <v>-0.01622725948779867</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
@@ -8361,22 +8361,22 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
         <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.1009520015738539</v>
+        <v>0.1466905120748278</v>
       </c>
       <c r="GA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.1557255390265962</v>
+        <v>-0.1310279476846191</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8399,43 +8399,43 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5414380825793781</v>
+        <v>0.4344364125144715</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1998426315185799</v>
+        <v>-0.2719983474765316</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.101758090918795</v>
+        <v>0.07629470632308546</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4557672996032627</v>
+        <v>0.5061476216267343</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2047312745740952</v>
+        <v>-0.342045803904772</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1221847607932054</v>
+        <v>0.01946474564423197</v>
       </c>
       <c r="O15" t="n">
         <v>-0</v>
@@ -8450,25 +8450,25 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1118068116948107</v>
+        <v>0.05752302179973198</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.001460895396549126</v>
+        <v>-0.005828584810237594</v>
       </c>
       <c r="W15" t="n">
-        <v>0.09104853323743617</v>
+        <v>-0.02064115355940295</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>-0</v>
@@ -8477,46 +8477,46 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1251939517270195</v>
+        <v>-0.01371126958515021</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.004436335133228469</v>
+        <v>-0.1321542928888284</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.03686746365945824</v>
+        <v>-0.006293312018987699</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.006439238803396014</v>
+        <v>0.07782464436775186</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.06467609694555809</v>
+        <v>-0.06197635131961714</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.07310391927083025</v>
+        <v>0.0652051386801235</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -8525,79 +8525,79 @@
         <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.3789954868876919</v>
+        <v>0.3296065135633128</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.02633273259850467</v>
+        <v>-0.1830932509732597</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1164103623256756</v>
+        <v>-0.1640713127728616</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05615716375677069</v>
+        <v>-0.03018238061942602</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.1006172633388391</v>
+        <v>-0.08305228176012089</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.133127453892922</v>
+        <v>0.03273070306124855</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.07498010493952958</v>
+        <v>-0.02571189310689207</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.02417959344799455</v>
+        <v>0.06003502814313842</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1991383967692761</v>
+        <v>-0.009052814460760561</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
@@ -8615,49 +8615,49 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.190343074555544</v>
+        <v>0.2381993522294053</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.02378606492855606</v>
+        <v>-0.1304512493708275</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0834530674275915</v>
+        <v>0.01303323132289085</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1061282572934357</v>
+        <v>-0.108824264562567</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02972664842584914</v>
+        <v>0.1232170769527551</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.004019122460763205</v>
+        <v>-0.03045129833238732</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,19 +8669,19 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.0668308996947365</v>
+        <v>-0.08703164619242708</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.08572472836114194</v>
+        <v>0.1642065029513283</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1512250895047044</v>
+        <v>0.03590659219824592</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8690,28 +8690,28 @@
         <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.09944817341697773</v>
+        <v>-0.1126173044669905</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.04446669319753591</v>
+        <v>0.1354615767442102</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.002995253504181955</v>
+        <v>-0.02336958322792555</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.02934540752715594</v>
+        <v>-0.06521589712944392</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.01509936110780266</v>
+        <v>0.04336713640401574</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01841549120728564</v>
+        <v>-0.03896592698562078</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
@@ -8747,73 +8747,73 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.01637021718569463</v>
+        <v>-0.01612998195275146</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1298020033018067</v>
+        <v>0.04641335455650931</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.04258183373368159</v>
+        <v>-0.03350129610425048</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.08367037895552656</v>
+        <v>-0.01628949892522291</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.006996178893644515</v>
+        <v>0.01732286432124232</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02734998987009152</v>
+        <v>-0.0469646858481217</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1354537407479001</v>
+        <v>-0.06246769724842955</v>
       </c>
       <c r="EH15" t="n">
         <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.06383510561344521</v>
+        <v>0.1029817197781215</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1024280963608441</v>
+        <v>-0.0071320035121878</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
@@ -8822,61 +8822,61 @@
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.07614687300648931</v>
+        <v>-0.07293853389588711</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.04797332510706878</v>
+        <v>0.03696105003391699</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.02029266126226174</v>
+        <v>-0.0348245696390904</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.09876900677585457</v>
+        <v>-0.1341173728055207</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.023924748977956</v>
+        <v>0.1476491035342978</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.006078731172317005</v>
+        <v>-0.02565776614487215</v>
       </c>
       <c r="FC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
@@ -8885,82 +8885,82 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.03378800482612862</v>
+        <v>0.1419320957454099</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.08480460414297032</v>
+        <v>-0.1830247598923699</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.05635082886660885</v>
+        <v>0.0265305704952359</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0001710445638036932</v>
+        <v>-0.1981515944315747</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.05266854784845921</v>
+        <v>0.1133786892844525</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.04405156077684232</v>
+        <v>0.05777765071323811</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0007208205210883847</v>
+        <v>-0.07279454409470555</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.07678241144524803</v>
+        <v>0.04474089845743433</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
